--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -334,12 +334,12 @@
   <commentList>
     <comment ref="B11" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 1/2004, de 21 de diciembre, de Horarios Comerciales (BOE-A-2004-21421), texto consolidado · «Última modificación: 17 de octubre de 2014» (Nuevo matiz que la lente no traía: el propio art. 5.1 da libertad plena también a los establecimientos situados «en zonas de gran afluenc...) · https://www.boe.es/buscar/act.php?id=BOE-A-2004-21421</t>
+        <t>Verificado el 12-09-2026 · Ley 1/2004, de 21 de diciembre, de Horarios Comerciales (BOE-A-2004-21421), texto consolidado · «Última modificación: 17 de octubre de 2014» (Nuevo matiz que la lente no traía: el propio art. 5.1 da libertad plena también a los establecimientos situados «en zonas de...) · https://www.boe.es/buscar/act.php?id=BOE-A-2004-21421</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B16" authorId="0" shapeId="0">
@@ -349,7 +349,7 @@
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno sería el 21 %, salvo que...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno ser...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
@@ -374,7 +374,7 @@
   <commentList>
     <comment ref="F11" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B23" authorId="0" shapeId="0">
@@ -414,7 +414,7 @@
     </comment>
     <comment ref="B68" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Dos límites del propio texto: queda fuera lo que tenga impacto en el patrimonio histórico-artístico o en el uso priv... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Arts.) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
   </commentList>
@@ -554,7 +554,7 @@
     </comment>
     <comment ref="B42" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno sería el 21 %, salvo que...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Lo que sigue abierto es el TIPO: el art. 91 no nombra los talleres, así que por la regla general del art. 90.Uno ser...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B48" authorId="0" shapeId="0">
